--- a/artfynd/S 1066-2025 artfynd.xlsx
+++ b/artfynd/S 1066-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY38"/>
+  <dimension ref="A1:AZ38"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -786,6 +791,11 @@
           <t>SCA Skog Naturvärdesinventering</t>
         </is>
       </c>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104441976</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -900,6 +910,11 @@
           <t>SCA Skog Naturvärdesinventering</t>
         </is>
       </c>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104441975</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -997,6 +1012,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134503642</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1094,6 +1114,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125572926</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1208,6 +1233,11 @@
           <t>SCA Skog Naturvärdesinventering</t>
         </is>
       </c>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104441978</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1305,6 +1335,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125572962</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1402,6 +1437,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134497040</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1504,6 +1544,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134503669</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1601,6 +1646,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134503672</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1698,6 +1748,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134503673</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1795,6 +1850,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134503674</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1892,6 +1952,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134503675</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -1989,6 +2054,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134503676</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2086,6 +2156,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134503677</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2183,6 +2258,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134503678</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2280,6 +2360,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134497420</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2377,6 +2462,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134503651</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2474,6 +2564,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134503652</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2571,6 +2666,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134503640</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2685,6 +2785,11 @@
           <t>SCA Skog Naturvärdesinventering</t>
         </is>
       </c>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104441977</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2782,6 +2887,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134503645</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -2879,6 +2989,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134503646</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -2976,6 +3091,11 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134503648</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3078,6 +3198,11 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134503635</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3186,6 +3311,11 @@
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134503682</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3283,6 +3413,11 @@
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134503630</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -3380,6 +3515,11 @@
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134503649</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -3482,6 +3622,11 @@
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134503653</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -3584,6 +3729,11 @@
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134503654</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -3686,6 +3836,11 @@
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134503655</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -3788,6 +3943,11 @@
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134503656</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -3890,6 +4050,11 @@
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134503657</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -3992,6 +4157,11 @@
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
+      <c r="AZ34" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134503659</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -4094,6 +4264,11 @@
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
+      <c r="AZ35" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134503660</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -4196,6 +4371,11 @@
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
+      <c r="AZ36" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134503661</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -4298,6 +4478,11 @@
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
+      <c r="AZ37" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134503663</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -4400,8 +4585,52 @@
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
+      <c r="AZ38" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134503664</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ36" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ37" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ38" r:id="rId37"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>